--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486363_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486363_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4618</v>
+        <v>6.1315</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6572</v>
+        <v>4.5401</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8046</v>
+        <v>1.5915</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0752</v>
+        <v>3.4691</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7916</v>
+        <v>-0.0092</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7164</v>
+        <v>3.4783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2418</v>
+        <v>3.4429</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8339</v>
+        <v>-0.2888</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5921</v>
+        <v>3.7317</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8334</v>
+        <v>0.0262</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9577</v>
+        <v>0.2796</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1243</v>
+        <v>-0.2534</v>
       </c>
       <c r="P2" t="n">
         <v>1.305</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7563</v>
+        <v>1.5526</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9824</v>
+        <v>1.0972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7739</v>
+        <v>0.4554</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6504</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8021</v>
+        <v>5.7796</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2106</v>
+        <v>3.975</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5915</v>
+        <v>1.8046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4691</v>
+        <v>1.0752</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0092</v>
+        <v>1.7916</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4783</v>
+        <v>-0.7164</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4429</v>
+        <v>0.2418</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2888</v>
+        <v>0.8339</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7317</v>
+        <v>-0.5921</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0262</v>
+        <v>0.8334</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2796</v>
+        <v>0.9577</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2534</v>
+        <v>-0.1243</v>
       </c>
       <c r="P3" t="n">
         <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2231</v>
+        <v>2.0741</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7677</v>
+        <v>1.3003</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4554</v>
+        <v>0.7739</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.6504</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2322</v>
+        <v>2.5983</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2154</v>
+        <v>0.5507</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0168</v>
+        <v>2.0476</v>
       </c>
       <c r="G4" t="n">
         <v>0.0707</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8341</v>
+        <v>1.2002</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2091</v>
+        <v>0.5444</v>
       </c>
       <c r="U4" t="n">
-        <v>0.625</v>
+        <v>0.6558</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8337</v>
+        <v>2.3539</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.2037</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9653</v>
+        <v>1.1502</v>
       </c>
       <c r="G5" t="n">
         <v>1.0973</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0461</v>
+        <v>0.4741</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2776</v>
+        <v>0.6129</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3237</v>
+        <v>-0.1388</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8072</v>
+        <v>1.8045</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0068</v>
+        <v>3.2711</v>
       </c>
       <c r="F6" t="n">
-        <v>1.814</v>
+        <v>-1.4666</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8189</v>
+        <v>1.1687</v>
       </c>
       <c r="H6" t="n">
-        <v>2.564</v>
+        <v>2.2477</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7451</v>
+        <v>-1.079</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7417</v>
+        <v>1.309</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4668</v>
+        <v>1.9011</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7251</v>
+        <v>-0.5921</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0772</v>
+        <v>-0.1403</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.3466</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0199</v>
+        <v>-0.4869</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7708</v>
+        <v>1.178</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4266</v>
+        <v>0.8544</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3442</v>
+        <v>0.3235</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.13</v>
+        <v>-2.0647</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1763</v>
+        <v>1.711</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4888</v>
+        <v>0.3285</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3125</v>
+        <v>1.3824</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1687</v>
+        <v>1.8189</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2477</v>
+        <v>2.564</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.079</v>
+        <v>-0.7451</v>
       </c>
       <c r="J7" t="n">
-        <v>1.309</v>
+        <v>1.7417</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9011</v>
+        <v>2.4668</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5921</v>
+        <v>-0.7251</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1403</v>
+        <v>0.0772</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3466</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4869</v>
+        <v>-0.0199</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.6525</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.5225</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.2175</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.7401</v>
-      </c>
       <c r="S7" t="n">
-        <v>0.5498</v>
+        <v>1.6746</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0721</v>
+        <v>0.7619</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4777</v>
+        <v>0.9127</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0647</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.3899</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7208</v>
+        <v>1.5533</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5718</v>
+        <v>-0.6778</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2927</v>
+        <v>2.231</v>
       </c>
       <c r="G8" t="n">
         <v>0.3249</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2209</v>
+        <v>1.0533</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8099</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0308</v>
+        <v>0.9692</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0914</v>
+        <v>0.2028</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3419</v>
+        <v>-1.5823</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2505</v>
+        <v>1.7852</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4293</v>
+        <v>0.6512</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6843</v>
+        <v>1.393</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7451</v>
+        <v>-0.7418</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3896</v>
+        <v>0.0154</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2222</v>
+        <v>0.3348</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1674</v>
+        <v>-0.3195</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0398</v>
+        <v>0.6358</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4621</v>
+        <v>1.0582</v>
       </c>
       <c r="O9" t="n">
         <v>-0.4224</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-2.1751</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-3.4801</v>
       </c>
       <c r="R9" t="n">
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8496</v>
+        <v>1.5517</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7487</v>
+        <v>0.3822</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1009</v>
+        <v>1.1695</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5832000000000001</v>
+        <v>0.1051</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0294</v>
+        <v>-1.4536</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4461</v>
+        <v>1.5587</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6512</v>
+        <v>1.4293</v>
       </c>
       <c r="H10" t="n">
-        <v>1.393</v>
+        <v>0.6843</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7418</v>
+        <v>0.7451</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0154</v>
+        <v>1.3896</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3348</v>
+        <v>0.2222</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3195</v>
+        <v>1.1674</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6358</v>
+        <v>0.0398</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0582</v>
+        <v>0.4621</v>
       </c>
       <c r="O10" t="n">
         <v>-0.4224</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.87</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-3.4801</v>
       </c>
       <c r="R10" t="n">
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.0461</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0649</v>
+        <v>0.6369</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8305</v>
+        <v>0.4092</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9899</v>
+        <v>-0.8704</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8189</v>
+        <v>-2.4837</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8291</v>
+        <v>1.6133</v>
       </c>
       <c r="G11" t="n">
         <v>0.1113</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9641</v>
+        <v>1.0836</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3305</v>
+        <v>0.0048</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2946</v>
+        <v>1.0788</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7602</v>
@@ -1348,10 +1348,10 @@
         <v>21.3696</v>
       </c>
       <c r="E12" t="n">
-        <v>7.671599999999997</v>
+        <v>7.671700000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>13.6981</v>
+        <v>13.6979</v>
       </c>
       <c r="G12" t="n">
         <v>11.2166</v>
@@ -1366,22 +1366,22 @@
         <v>8.2293</v>
       </c>
       <c r="K12" t="n">
-        <v>8.8986</v>
+        <v>8.898600000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6692999999999996</v>
+        <v>-0.6692999999999998</v>
       </c>
       <c r="M12" t="n">
         <v>2.9875</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1987</v>
+        <v>5.198700000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-2.2114</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1749</v>
+        <v>2.174899999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.9629</v>
@@ -1390,13 +1390,13 @@
         <v>14.1376</v>
       </c>
       <c r="S12" t="n">
-        <v>12.8882</v>
+        <v>12.8883</v>
       </c>
       <c r="T12" t="n">
-        <v>6.2789</v>
+        <v>6.279100000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>6.609299999999999</v>
+        <v>6.6092</v>
       </c>
       <c r="V12" t="n">
         <v>-4.9103</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3771</v>
+        <v>4.7843</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8715</v>
+        <v>3.5304</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5056</v>
+        <v>1.2539</v>
       </c>
       <c r="G13" t="n">
         <v>2.1114</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6784</v>
+        <v>0.0856</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2762</v>
+        <v>-0.0649</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4022</v>
+        <v>0.1505</v>
       </c>
       <c r="V13" t="n">
         <v>1.4997</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5426</v>
+        <v>1.7661</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3325</v>
+        <v>1.556</v>
       </c>
       <c r="F14" t="n">
         <v>0.2101</v>
@@ -1546,10 +1546,10 @@
         <v>0.435</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.447</v>
+        <v>-0.2235</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U14" t="n">
         <v>-0.1046</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6731</v>
+        <v>1.0572</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0346</v>
+        <v>1.1464</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3615</v>
+        <v>-0.0892</v>
       </c>
       <c r="G15" t="n">
         <v>0.8769</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2913</v>
+        <v>-0.9073</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1644</v>
+        <v>-1.0527</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1269</v>
+        <v>0.1454</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0204</v>
+        <v>0.3428</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3502</v>
+        <v>0.462</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3298</v>
+        <v>-0.1191</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4981</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0464</v>
+        <v>-0.724</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3615</v>
+        <v>-0.1508</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1575</v>
+        <v>-1.8503</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.259</v>
+        <v>-1.0876</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1015</v>
+        <v>-0.7627</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6654</v>
+        <v>-1.0055</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.9196</v>
+        <v>-1.1162</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2542</v>
+        <v>0.1108</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6748</v>
+        <v>0.5191</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.2867</v>
+        <v>-0.2674</v>
       </c>
       <c r="L17" t="n">
-        <v>0.612</v>
+        <v>0.7865</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9907</v>
+        <v>-1.5246</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6328</v>
+        <v>-0.8488</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3578</v>
+        <v>-0.6758</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4046</v>
+        <v>-1.4751</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>-0.6922</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5826</v>
+        <v>-0.7829</v>
       </c>
       <c r="V17" t="n">
-        <v>1.695</v>
+        <v>0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>0.3904</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6349</v>
+        <v>-2.1433</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8063</v>
+        <v>-2.1473</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8286</v>
+        <v>0.004</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9278</v>
+        <v>-2.6654</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6632</v>
+        <v>-2.9196</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2646</v>
+        <v>0.2542</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3954</v>
+        <v>-1.6748</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0182</v>
+        <v>-2.2867</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4136</v>
+        <v>0.612</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5324</v>
+        <v>-0.9907</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6814</v>
+        <v>-0.6328</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>-0.3578</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5772</v>
+        <v>-1.3904</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.411</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1662</v>
+        <v>-0.6802</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.695</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6428</v>
+        <v>-2.3777</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4229</v>
+        <v>-1.6832</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2199</v>
+        <v>-0.6945</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0055</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1162</v>
+        <v>-1.3657</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1108</v>
+        <v>0.5618</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5191</v>
+        <v>0.0824</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2674</v>
+        <v>-0.4348</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7865</v>
+        <v>0.5172</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5246</v>
+        <v>-0.8863</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8488</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6758</v>
+        <v>0.0446</v>
       </c>
       <c r="P19" t="n">
-        <v>0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2676</v>
+        <v>-1.3988</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0274</v>
+        <v>-0.9157</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2402</v>
+        <v>-0.4831</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3904</v>
+        <v>1.3252</v>
       </c>
       <c r="X19" t="n">
         <v>-0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8851</v>
+        <v>-2.5784</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.795</v>
+        <v>-1.8063</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0901</v>
+        <v>-0.772</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-1.9278</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3657</v>
+        <v>-0.6632</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5618</v>
+        <v>-1.2646</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0824</v>
+        <v>-1.3954</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4348</v>
+        <v>0.0182</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5172</v>
+        <v>-1.4136</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8863</v>
+        <v>-0.5324</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.6814</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0446</v>
+        <v>0.149</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9061</v>
+        <v>-0.5206</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0274</v>
+        <v>-0.411</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8787</v>
+        <v>-0.1097</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7953</v>
+        <v>-4.7773</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8961</v>
+        <v>-3.1196</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8992</v>
+        <v>-1.6577</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6405</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1749</v>
+        <v>-1.1569</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0601</v>
+        <v>-0.1634</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.235</v>
+        <v>-0.9935</v>
       </c>
       <c r="V21" t="n">
         <v>1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.868</v>
+        <v>-6.1621</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9292</v>
+        <v>-5.8174</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0611</v>
+        <v>-0.3447</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9734</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1546</v>
+        <v>-1.4487</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0959</v>
+        <v>-0.9842</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0587</v>
+        <v>-0.4645</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.9991</v>
+        <v>-7.9407</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1782</v>
+        <v>-4.7312</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8209</v>
+        <v>-3.2095</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4625</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.2969</v>
+        <v>-2.2385</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3699</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.9269</v>
+        <v>-1.3156</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4997</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-21.3695</v>
+        <v>-19.8794</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.6979</v>
+        <v>-13.6978</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.6717</v>
+        <v>-6.1814</v>
       </c>
       <c r="G24" t="n">
         <v>-11.2167</v>
@@ -2299,22 +2299,22 @@
         <v>2.8806</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9873</v>
+        <v>-2.987300000000001</v>
       </c>
       <c r="K24" t="n">
         <v>-5.1988</v>
       </c>
       <c r="L24" t="n">
-        <v>2.2115</v>
+        <v>2.211499999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-8.2294</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.898400000000001</v>
+        <v>-8.898399999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6692</v>
+        <v>0.6692000000000002</v>
       </c>
       <c r="P24" t="n">
         <v>-2.1752</v>
@@ -2326,13 +2326,13 @@
         <v>11.9628</v>
       </c>
       <c r="S24" t="n">
-        <v>-12.8882</v>
+        <v>-11.3982</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.6092</v>
+        <v>-6.609400000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.2791</v>
+        <v>-4.789000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>4.910399999999999</v>
